--- a/repo/skin.nedflix/Things to add and fix.xlsx
+++ b/repo/skin.nedflix/Things to add and fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deta\AppData\Roaming\Kodi\addons\skin.nedflix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDF6212-88F7-4EFA-9AB1-9FA93E01F079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991ABCB0-0D26-4419-86AC-FB5447C22505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8E1D553F-56F2-46D7-AA49-3E56ED8BAEF5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>To add/fix</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>make watched overlay work on wrestling widgets</t>
+  </si>
+  <si>
+    <t>remember which episode is selected when going back to episode/season view after watching an episode</t>
   </si>
 </sst>
 </file>
@@ -501,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE179428-6FDC-4F92-8486-7C268F2BD909}">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="134.28515625" customWidth="1"/>
@@ -567,6 +570,11 @@
         <v>9</v>
       </c>
     </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
